--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_45.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3800552.46665163</v>
+        <v>3801656.990167137</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13593507.1466832</v>
+        <v>13593507.14668318</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13593507.1466832</v>
+        <v>13593507.14668318</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6591.459428723209</v>
+        <v>6591.459428722918</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6591.459428723209</v>
+        <v>6591.459428722918</v>
       </c>
     </row>
     <row r="11">
@@ -666,7 +666,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>6.843035168803288</v>
       </c>
       <c r="G2" t="n">
         <v>3.343301935257443</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.953406460792503</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>85.41253966161941</v>
@@ -723,7 +723,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828053</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -739,22 +739,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>144.6926477280658</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>241.3258960574012</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
         <v>62.44885845517734</v>
@@ -790,7 +790,7 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>5.296708396048877</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
         <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>120.2823347832845</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.5184388018132</v>
@@ -1027,19 +1027,19 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>304.1437874104409</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1146,10 +1146,10 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>5.722467174369123</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1380,10 +1380,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.36239741264433</v>
+        <v>78.40634055685268</v>
       </c>
       <c r="H11" t="n">
-        <v>69.76731541557497</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1447,16 +1447,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
         <v>3.993158516536766</v>
@@ -1465,7 +1465,7 @@
         <v>3.959653224156966</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>179.932929367851</v>
@@ -1501,7 +1501,7 @@
         <v>81.34934068921194</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16125598660182</v>
+        <v>391.8917783838309</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1510,10 +1510,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>204.2171562283915</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1611,16 +1611,16 @@
         <v>89.33915573984979</v>
       </c>
       <c r="E14" t="n">
-        <v>83.36328960686865</v>
+        <v>80.407232751077</v>
       </c>
       <c r="F14" t="n">
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H14" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>139.1041209967824</v>
+        <v>142.0601778525742</v>
       </c>
       <c r="T14" t="n">
         <v>259.5690792160011</v>
       </c>
       <c r="U14" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1696,10 +1696,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1726,25 +1726,25 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R15" t="n">
         <v>179.932929367851</v>
       </c>
       <c r="S15" t="n">
-        <v>452.7003678891396</v>
+        <v>237.0547846721435</v>
       </c>
       <c r="T15" t="n">
-        <v>402.3493406892119</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U15" t="n">
-        <v>262.3205227657455</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>419.8627394453875</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M16" t="n">
         <v>101.5443818943532</v>
@@ -1799,19 +1799,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O16" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P16" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R16" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S16" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>78.40634055685268</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H17" t="n">
-        <v>72.7233722713666</v>
+        <v>69.76731541557517</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U17" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
         <v>21.67209722191262</v>
@@ -1933,10 +1933,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H18" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1963,31 +1963,31 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>285.2873461508548</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S18" t="n">
         <v>131.7003678891396</v>
       </c>
       <c r="T18" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>78.39139276613435</v>
+        <v>261.5506595452779</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M19" t="n">
         <v>101.5443818943532</v>
@@ -2036,19 +2036,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O19" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P19" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q19" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R19" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S19" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>40.09991244551929</v>
@@ -2164,10 +2164,10 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
         <v>3.993158516536766</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>179.932929367851</v>
@@ -2209,22 +2209,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T21" t="n">
-        <v>186.703757472216</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U21" t="n">
-        <v>400.1612559866018</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>276.669933970664</v>
       </c>
       <c r="W21" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2316,7 +2316,7 @@
         <v>160.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>125.5185213872023</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D23" t="n">
         <v>89.33915573984979</v>
@@ -2328,7 +2328,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.36239741264433</v>
+        <v>78.40634055685268</v>
       </c>
       <c r="H23" t="n">
         <v>72.7233722713666</v>
@@ -2404,16 +2404,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G24" t="n">
         <v>3.993158516536766</v>
       </c>
       <c r="H24" t="n">
-        <v>3.959653224156966</v>
+        <v>238.8853256252464</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,13 +2440,13 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R24" t="n">
-        <v>285.2873461508548</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S24" t="n">
-        <v>452.7003678891396</v>
+        <v>131.7003678891396</v>
       </c>
       <c r="T24" t="n">
-        <v>402.3493406892119</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U24" t="n">
         <v>79.16125598660182</v>
@@ -2455,13 +2455,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2565,10 +2565,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H26" t="n">
-        <v>73.64811541557496</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S26" t="n">
         <v>142.0601778525742</v>
@@ -2607,7 +2607,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U26" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2632,22 +2632,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H27" t="n">
-        <v>109.3140700071609</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R27" t="n">
-        <v>500.932929367851</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S27" t="n">
-        <v>452.7003678891396</v>
+        <v>237.0547846721435</v>
       </c>
       <c r="T27" t="n">
-        <v>81.34934068921194</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U27" t="n">
-        <v>400.1612559866018</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M28" t="n">
         <v>101.5443818943532</v>
@@ -2747,19 +2747,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P28" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R28" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S28" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2866,28 +2866,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>246.7158234254702</v>
       </c>
       <c r="C30" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>324.9931585165368</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H30" t="n">
         <v>3.959653224156966</v>
       </c>
       <c r="I30" t="n">
-        <v>183.1592667791439</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>500.932929367851</v>
+        <v>179.932929367851</v>
       </c>
       <c r="S30" t="n">
         <v>131.7003678891396</v>
@@ -3042,7 +3042,7 @@
         <v>81.36239741264436</v>
       </c>
       <c r="H32" t="n">
-        <v>73.64811541560218</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.701199264265597e-11</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>142.0601778525742</v>
+        <v>142.9849209967825</v>
       </c>
       <c r="T32" t="n">
         <v>259.5690792160011</v>
@@ -3106,7 +3106,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>223.2591792246629</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
@@ -3118,13 +3118,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>316.7236809137661</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H33" t="n">
-        <v>324.959653224157</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I33" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3154,7 +3154,7 @@
         <v>179.932929367851</v>
       </c>
       <c r="S33" t="n">
-        <v>452.7003678891396</v>
+        <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
         <v>81.34934068921193</v>
@@ -3166,13 +3166,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>136.9993129555745</v>
+        <v>132.4136560997827</v>
       </c>
       <c r="C35" t="n">
         <v>104.4745782429939</v>
@@ -3276,10 +3276,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>57.36239741264433</v>
+        <v>57.36239741264435</v>
       </c>
       <c r="H35" t="n">
-        <v>48.7233722713666</v>
+        <v>48.72337227136661</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>113.4745209967823</v>
+        <v>118.0601778525742</v>
       </c>
       <c r="T35" t="n">
         <v>235.5690792160011</v>
       </c>
       <c r="U35" t="n">
-        <v>304.109698558661</v>
+        <v>304.1096985586609</v>
       </c>
       <c r="V35" t="n">
         <v>284.8510241668239</v>
@@ -3355,13 +3355,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>18.48830454455231</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R36" t="n">
         <v>155.932929367851</v>
@@ -3394,7 +3394,7 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T36" t="n">
-        <v>173.6493367133598</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U36" t="n">
         <v>400.1612559866018</v>
@@ -3403,13 +3403,13 @@
         <v>69.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>432.3731429098285</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X36" t="n">
         <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>77.54438189435319</v>
+        <v>77.54438189435318</v>
       </c>
       <c r="N37" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O37" t="n">
-        <v>207.000383751146</v>
+        <v>207.0003837511461</v>
       </c>
       <c r="P37" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q37" t="n">
-        <v>328.4422664255979</v>
+        <v>328.442266425598</v>
       </c>
       <c r="R37" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S37" t="n">
-        <v>6.468578063511188</v>
+        <v>6.468578063511176</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>136.9993129555745</v>
+        <v>132.4136560997827</v>
       </c>
       <c r="C38" t="n">
         <v>104.4745782429939</v>
@@ -3513,7 +3513,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>52.7767405568525</v>
+        <v>57.36239741264435</v>
       </c>
       <c r="H38" t="n">
         <v>48.72337227136661</v>
@@ -3577,16 +3577,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,13 +3625,13 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R39" t="n">
-        <v>333.3562471925395</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S39" t="n">
-        <v>107.7003678891396</v>
+        <v>113.8399860980593</v>
       </c>
       <c r="T39" t="n">
-        <v>402.3493406892119</v>
+        <v>57.34934068921193</v>
       </c>
       <c r="U39" t="n">
         <v>55.16125598660184</v>
@@ -3750,7 +3750,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>57.36239741264435</v>
+        <v>52.7767405568525</v>
       </c>
       <c r="H41" t="n">
         <v>48.72337227136661</v>
@@ -3801,7 +3801,7 @@
         <v>293.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>242.6961766048758</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>166.3174326828064</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>76.25280776477661</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.807578418171033e-11</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>500.932929367851</v>
+        <v>155.932929367851</v>
       </c>
       <c r="S42" t="n">
-        <v>107.7003678891396</v>
+        <v>452.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>402.3493406892119</v>
+        <v>133.6021484540392</v>
       </c>
       <c r="U42" t="n">
         <v>400.1612559866018</v>
       </c>
       <c r="V42" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>54.39139276613435</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>361.0999124455193</v>
@@ -4060,7 +4060,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>78.58071054292171</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.25280776477643</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>155.932929367851</v>
       </c>
       <c r="S45" t="n">
-        <v>452.7003678891396</v>
+        <v>107.7003678891396</v>
       </c>
       <c r="T45" t="n">
         <v>57.34934068921194</v>
@@ -4120,7 +4120,7 @@
         <v>74.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C2" t="n">
-        <v>56.89417848844992</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D2" t="n">
-        <v>46.450586832036</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E2" t="n">
-        <v>42.04322359277474</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F2" t="n">
         <v>37.10420469579307</v>
@@ -4330,7 +4330,7 @@
         <v>517.0145614572864</v>
       </c>
       <c r="M2" t="n">
-        <v>696.8157936111288</v>
+        <v>887.2745614572864</v>
       </c>
       <c r="N2" t="n">
         <v>1067.075793611129</v>
@@ -4345,28 +4345,28 @@
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.026862160816</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.751569573321</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.021277892776</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3160547407863</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1433030571258</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>496.3620141874817</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1379399847871</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.6960887900342</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>593.1868263490119</v>
+        <v>848.1470649053622</v>
       </c>
       <c r="C3" t="n">
-        <v>593.1868263490119</v>
+        <v>848.1470649053622</v>
       </c>
       <c r="D3" t="n">
-        <v>241.7346173614335</v>
+        <v>848.1470649053622</v>
       </c>
       <c r="E3" t="n">
-        <v>241.7346173614335</v>
+        <v>848.1470649053622</v>
       </c>
       <c r="F3" t="n">
-        <v>241.7346173614335</v>
+        <v>505.0801534529613</v>
       </c>
       <c r="G3" t="n">
-        <v>241.7346173614335</v>
+        <v>176.2741042557734</v>
       </c>
       <c r="H3" t="n">
-        <v>241.7346173614335</v>
+        <v>176.2741042557734</v>
       </c>
       <c r="I3" t="n">
         <v>30.1199146314645</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.738421006376</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1105.974889635264</v>
+        <v>1361.132890099179</v>
       </c>
       <c r="S3" t="n">
-        <v>1042.895234630035</v>
+        <v>1298.053235093949</v>
       </c>
       <c r="T3" t="n">
-        <v>1038.385361244705</v>
+        <v>1293.54336170862</v>
       </c>
       <c r="U3" t="n">
-        <v>660.6075834669273</v>
+        <v>1293.345599801055</v>
       </c>
       <c r="V3" t="n">
-        <v>645.9503438795332</v>
+        <v>1278.688360213661</v>
       </c>
       <c r="W3" t="n">
-        <v>613.2501995261711</v>
+        <v>1245.988215860299</v>
       </c>
       <c r="X3" t="n">
-        <v>593.1868263490119</v>
+        <v>1225.92484268314</v>
       </c>
       <c r="Y3" t="n">
-        <v>593.1868263490119</v>
+        <v>848.1470649053622</v>
       </c>
     </row>
     <row r="4">
@@ -4455,25 +4455,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
       <c r="C4" t="n">
-        <v>344.783355469044</v>
+        <v>221.612662066494</v>
       </c>
       <c r="D4" t="n">
-        <v>448.2753239533965</v>
+        <v>221.612662066494</v>
       </c>
       <c r="E4" t="n">
-        <v>566.1042281648096</v>
+        <v>339.441566277907</v>
       </c>
       <c r="F4" t="n">
-        <v>690.465200756745</v>
+        <v>463.8025388698425</v>
       </c>
       <c r="G4" t="n">
-        <v>844.0556469714992</v>
+        <v>617.3929850845966</v>
       </c>
       <c r="H4" t="n">
-        <v>1015.207095409585</v>
+        <v>788.5444335226827</v>
       </c>
       <c r="I4" t="n">
         <v>1015.207095409585</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
       <c r="U4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
       <c r="V4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
       <c r="W4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
       <c r="X4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
       <c r="Y4" t="n">
-        <v>218.7813496506081</v>
+        <v>221.612662066494</v>
       </c>
     </row>
     <row r="5">
@@ -4549,10 +4549,10 @@
         <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.72713203391686</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
@@ -4561,22 +4561,22 @@
         <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>452.3245884924623</v>
+        <v>632.1258206463046</v>
       </c>
       <c r="L5" t="n">
-        <v>517.0145614572864</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M5" t="n">
-        <v>887.2745614572864</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="N5" t="n">
-        <v>1257.534561457286</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1257.534561457286</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1316.198767846158</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>394.6673863086054</v>
+        <v>502.869516849482</v>
       </c>
       <c r="C6" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1349.538506374912</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1214.671396474091</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1151.591741468861</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>1147.081868083532</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>839.8659212042986</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>825.2086816169045</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W6" t="n">
-        <v>792.5085372635424</v>
+        <v>900.710667804419</v>
       </c>
       <c r="X6" t="n">
-        <v>772.4451640863832</v>
+        <v>880.6472946272598</v>
       </c>
       <c r="Y6" t="n">
-        <v>394.6673863086054</v>
+        <v>880.6472946272598</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1023.050610806278</v>
+        <v>1021.390962989494</v>
       </c>
       <c r="C7" t="n">
-        <v>1023.050610806278</v>
+        <v>1147.392968807929</v>
       </c>
       <c r="D7" t="n">
-        <v>1023.050610806278</v>
+        <v>1260.712112932929</v>
       </c>
       <c r="E7" t="n">
-        <v>1023.050610806278</v>
+        <v>1378.541017144342</v>
       </c>
       <c r="F7" t="n">
-        <v>1023.050610806278</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="G7" t="n">
-        <v>1023.050610806278</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H7" t="n">
-        <v>1023.050610806278</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I7" t="n">
-        <v>1249.71327269318</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1249.71327269318</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1381.441257449721</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
         <v>1385.467095409585</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.37478771712392</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7973598420842</v>
+        <v>276.4812224743522</v>
       </c>
       <c r="V7" t="n">
-        <v>704.6187527280301</v>
+        <v>475.3026153602981</v>
       </c>
       <c r="W7" t="n">
-        <v>876.5096709877075</v>
+        <v>647.1935336199756</v>
       </c>
       <c r="X7" t="n">
-        <v>1023.050610806278</v>
+        <v>798.2243246441691</v>
       </c>
       <c r="Y7" t="n">
-        <v>1023.050610806278</v>
+        <v>909.6336253232014</v>
       </c>
     </row>
     <row r="8">
@@ -4789,7 +4789,7 @@
         <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4801,10 +4801,10 @@
         <v>770.4399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>835.1299729648241</v>
+        <v>1140.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1205.389972964824</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="N8" t="n">
         <v>1437.335793611129</v>
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1138.949762690933</v>
+        <v>253.0866383453244</v>
       </c>
       <c r="C10" t="n">
-        <v>1138.949762690933</v>
+        <v>379.0886441637601</v>
       </c>
       <c r="D10" t="n">
-        <v>1138.949762690933</v>
+        <v>492.4077882887602</v>
       </c>
       <c r="E10" t="n">
-        <v>1138.949762690933</v>
+        <v>610.2366925001733</v>
       </c>
       <c r="F10" t="n">
-        <v>1138.949762690933</v>
+        <v>734.5976650921087</v>
       </c>
       <c r="G10" t="n">
-        <v>1138.949762690933</v>
+        <v>888.1881113068629</v>
       </c>
       <c r="H10" t="n">
-        <v>1138.949762690933</v>
+        <v>1059.339559744949</v>
       </c>
       <c r="I10" t="n">
-        <v>1138.949762690933</v>
+        <v>1286.002221631852</v>
       </c>
       <c r="J10" t="n">
-        <v>1249.71327269318</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1381.441257449721</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
         <v>1385.467095409585</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.37478771712392</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>505.7973598420842</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>704.6187527280301</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>876.5096709877075</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>1027.540462011901</v>
+        <v>29.92</v>
       </c>
       <c r="Y10" t="n">
-        <v>1138.949762690933</v>
+        <v>141.3293006790323</v>
       </c>
     </row>
     <row r="11">
@@ -5023,7 +5023,7 @@
         <v>204.4962755840599</v>
       </c>
       <c r="G11" t="n">
-        <v>122.3120357733081</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H11" t="n">
         <v>51.84</v>
@@ -5035,19 +5035,19 @@
         <v>560.3618942939371</v>
       </c>
       <c r="K11" t="n">
-        <v>736.0334691180577</v>
+        <v>1201.881894293937</v>
       </c>
       <c r="L11" t="n">
-        <v>953.9695916306206</v>
+        <v>1419.8180168065</v>
       </c>
       <c r="M11" t="n">
-        <v>1595.489591630623</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="N11" t="n">
-        <v>1595.489591630623</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O11" t="n">
-        <v>1758.63139788795</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P11" t="n">
         <v>2004.265727912157</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.030657215864</v>
+        <v>685.9081767935553</v>
       </c>
       <c r="C12" t="n">
-        <v>1100.525695149683</v>
+        <v>321.1607904849499</v>
       </c>
       <c r="D12" t="n">
-        <v>749.0734861621042</v>
+        <v>293.9510057397957</v>
       </c>
       <c r="E12" t="n">
-        <v>402.9400546248188</v>
+        <v>272.0599984449345</v>
       </c>
       <c r="F12" t="n">
-        <v>59.87314317241791</v>
+        <v>253.2355112349579</v>
       </c>
       <c r="G12" t="n">
-        <v>55.83964972137068</v>
+        <v>249.2020177839106</v>
       </c>
       <c r="H12" t="n">
-        <v>51.84</v>
+        <v>245.20236806254</v>
       </c>
       <c r="I12" t="n">
         <v>51.84</v>
@@ -5132,31 +5132,31 @@
         <v>2253.149505368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S12" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T12" t="n">
-        <v>1777.606588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U12" t="n">
-        <v>1697.645723622128</v>
+        <v>1460.347064631128</v>
       </c>
       <c r="V12" t="n">
-        <v>1603.190504236754</v>
+        <v>1365.891845245754</v>
       </c>
       <c r="W12" t="n">
-        <v>1490.692380085412</v>
+        <v>1253.393721094413</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.412424299158</v>
+        <v>1153.532368119274</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.22919928286</v>
+        <v>750.1067188605518</v>
       </c>
     </row>
     <row r="13">
@@ -5178,16 +5178,16 @@
         <v>809.1073267949506</v>
       </c>
       <c r="F13" t="n">
-        <v>855.2582993868861</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G13" t="n">
-        <v>931.0743456016402</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J13" t="n">
         <v>1510.983618808348</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.4384060421568</v>
+        <v>593.4524900262056</v>
       </c>
       <c r="C14" t="n">
-        <v>466.6661047866074</v>
+        <v>463.6801887706562</v>
       </c>
       <c r="D14" t="n">
-        <v>376.4245333322136</v>
+        <v>373.4386173162624</v>
       </c>
       <c r="E14" t="n">
-        <v>292.2191902949726</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F14" t="n">
-        <v>207.4821916000111</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G14" t="n">
         <v>125.2979517892592</v>
@@ -5269,25 +5269,25 @@
         <v>51.84</v>
       </c>
       <c r="J14" t="n">
-        <v>560.3618942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K14" t="n">
-        <v>736.0334691180577</v>
+        <v>310.0317798977626</v>
       </c>
       <c r="L14" t="n">
-        <v>953.9695916306206</v>
+        <v>947.509243836214</v>
       </c>
       <c r="M14" t="n">
-        <v>953.9695916306206</v>
+        <v>1589.029243836214</v>
       </c>
       <c r="N14" t="n">
-        <v>953.9695916306206</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O14" t="n">
-        <v>1362.745727912154</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P14" t="n">
-        <v>2004.265727912157</v>
+        <v>2592</v>
       </c>
       <c r="Q14" t="n">
         <v>2592</v>
@@ -5296,25 +5296,25 @@
         <v>2592</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.490786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.299797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U14" t="n">
-        <v>1857.875859826824</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V14" t="n">
-        <v>1545.905128345183</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.325859677559</v>
+        <v>1222.339943661608</v>
       </c>
       <c r="X14" t="n">
-        <v>951.3038056768851</v>
+        <v>948.3178896609338</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.0639746841513</v>
+        <v>756.0780586682001</v>
       </c>
     </row>
     <row r="15">
@@ -5333,13 +5333,13 @@
         <v>100.5886376772558</v>
       </c>
       <c r="E15" t="n">
-        <v>78.69763038239458</v>
+        <v>78.69763038239455</v>
       </c>
       <c r="F15" t="n">
-        <v>59.87314317241794</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G15" t="n">
-        <v>55.83964972137069</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H15" t="n">
         <v>51.84</v>
@@ -5369,28 +5369,28 @@
         <v>2253.149505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.149505368536</v>
+        <v>2174.558747796677</v>
       </c>
       <c r="R15" t="n">
-        <v>2071.399071663636</v>
+        <v>1992.808314091777</v>
       </c>
       <c r="S15" t="n">
-        <v>1614.125972785717</v>
+        <v>1753.359036645168</v>
       </c>
       <c r="T15" t="n">
-        <v>1207.712497342069</v>
+        <v>1671.187985443944</v>
       </c>
       <c r="U15" t="n">
-        <v>942.7422723261641</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V15" t="n">
-        <v>848.2870529407902</v>
+        <v>1172.529477183214</v>
       </c>
       <c r="W15" t="n">
-        <v>735.7889287894483</v>
+        <v>735.7889287894482</v>
       </c>
       <c r="X15" t="n">
-        <v>311.6851515718851</v>
+        <v>311.685151571885</v>
       </c>
       <c r="Y15" t="n">
         <v>232.5019265555877</v>
@@ -5448,10 +5448,10 @@
         <v>819.8981109568782</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.8958216380923</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R16" t="n">
-        <v>82.61634147829412</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S16" t="n">
         <v>51.84</v>
@@ -5466,13 +5466,13 @@
         <v>453.3389250109063</v>
       </c>
       <c r="W16" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X16" t="n">
-        <v>614.7122373437168</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y16" t="n">
-        <v>647.911538022749</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="17">
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>593.4524900262056</v>
+        <v>593.4524900262059</v>
       </c>
       <c r="C17" t="n">
-        <v>463.6801887706562</v>
+        <v>463.6801887706564</v>
       </c>
       <c r="D17" t="n">
-        <v>373.4386173162624</v>
+        <v>373.4386173162627</v>
       </c>
       <c r="E17" t="n">
-        <v>289.2332742790214</v>
+        <v>289.2332742790216</v>
       </c>
       <c r="F17" t="n">
-        <v>204.4962755840599</v>
+        <v>204.4962755840601</v>
       </c>
       <c r="G17" t="n">
-        <v>125.2979517892592</v>
+        <v>122.3120357733083</v>
       </c>
       <c r="H17" t="n">
         <v>51.84</v>
@@ -5509,22 +5509,22 @@
         <v>560.3618942939371</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.881894293937</v>
+        <v>736.0334691180577</v>
       </c>
       <c r="L17" t="n">
-        <v>1843.401894293937</v>
+        <v>1377.553469118058</v>
       </c>
       <c r="M17" t="n">
-        <v>2230.549243836214</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="N17" t="n">
-        <v>2230.549243836214</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O17" t="n">
-        <v>2393.691050093541</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P17" t="n">
-        <v>2592</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q17" t="n">
         <v>2592</v>
@@ -5539,7 +5539,7 @@
         <v>2186.313881748914</v>
       </c>
       <c r="U17" t="n">
-        <v>1854.889943810872</v>
+        <v>1854.889943810873</v>
       </c>
       <c r="V17" t="n">
         <v>1542.919212329232</v>
@@ -5548,10 +5548,10 @@
         <v>1222.339943661608</v>
       </c>
       <c r="X17" t="n">
-        <v>948.3178896609338</v>
+        <v>948.317889660934</v>
       </c>
       <c r="Y17" t="n">
-        <v>756.0780586682001</v>
+        <v>756.0780586682004</v>
       </c>
     </row>
     <row r="18">
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>816.7882329734396</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C18" t="n">
-        <v>452.0408466648342</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D18" t="n">
         <v>100.5886376772558</v>
       </c>
       <c r="E18" t="n">
-        <v>78.69763038239455</v>
+        <v>78.69763038239458</v>
       </c>
       <c r="F18" t="n">
-        <v>59.87314317241791</v>
+        <v>59.87314317241794</v>
       </c>
       <c r="G18" t="n">
-        <v>55.83964972137068</v>
+        <v>55.83964972137069</v>
       </c>
       <c r="H18" t="n">
         <v>51.84</v>
@@ -5606,31 +5606,31 @@
         <v>2253.149505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1886.389711280662</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S18" t="n">
-        <v>1753.359036645168</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T18" t="n">
-        <v>1671.187985443944</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1591.227120811013</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V18" t="n">
-        <v>1496.771901425639</v>
+        <v>1357.538837566188</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.273777274297</v>
+        <v>920.7982891724216</v>
       </c>
       <c r="X18" t="n">
-        <v>1284.412424299158</v>
+        <v>496.6945119548584</v>
       </c>
       <c r="Y18" t="n">
-        <v>1205.22919928286</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="19">
@@ -5685,10 +5685,10 @@
         <v>819.8981109568782</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.8958216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R19" t="n">
-        <v>82.61634147829413</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S19" t="n">
         <v>51.84</v>
@@ -5743,22 +5743,22 @@
         <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>560.3618942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K20" t="n">
-        <v>1201.881894293937</v>
+        <v>310.0317798977626</v>
       </c>
       <c r="L20" t="n">
-        <v>1419.8180168065</v>
+        <v>527.9679024103255</v>
       </c>
       <c r="M20" t="n">
-        <v>1419.8180168065</v>
+        <v>1169.487902410326</v>
       </c>
       <c r="N20" t="n">
-        <v>1419.8180168065</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O20" t="n">
-        <v>1582.959823063827</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P20" t="n">
         <v>2004.265727912157</v>
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>816.7882329734394</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C21" t="n">
-        <v>776.2832709072584</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D21" t="n">
-        <v>749.0734861621042</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E21" t="n">
-        <v>402.9400546248188</v>
+        <v>78.69763038239455</v>
       </c>
       <c r="F21" t="n">
         <v>59.87314317241791</v>
@@ -5843,31 +5843,31 @@
         <v>2253.149505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1671.187985443943</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U21" t="n">
-        <v>1266.984696568588</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V21" t="n">
-        <v>1172.529477183214</v>
+        <v>1496.771901425639</v>
       </c>
       <c r="W21" t="n">
         <v>1060.031353031872</v>
       </c>
       <c r="X21" t="n">
-        <v>960.1700000567333</v>
+        <v>960.1700000567336</v>
       </c>
       <c r="Y21" t="n">
-        <v>880.986775040436</v>
+        <v>556.744350798012</v>
       </c>
     </row>
     <row r="22">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.5872726401018</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C22" t="n">
-        <v>734.3792784585376</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D22" t="n">
         <v>764.360025632477</v>
@@ -5946,7 +5946,7 @@
         <v>619.8406342947774</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.0399349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="23">
@@ -5959,16 +5959,16 @@
         <v>593.4524900262056</v>
       </c>
       <c r="C23" t="n">
-        <v>466.6661047866073</v>
+        <v>463.6801887706562</v>
       </c>
       <c r="D23" t="n">
-        <v>376.4245333322136</v>
+        <v>373.4386173162624</v>
       </c>
       <c r="E23" t="n">
-        <v>292.2191902949725</v>
+        <v>289.2332742790214</v>
       </c>
       <c r="F23" t="n">
-        <v>207.482191600011</v>
+        <v>204.4962755840599</v>
       </c>
       <c r="G23" t="n">
         <v>125.2979517892592</v>
@@ -5986,19 +5986,19 @@
         <v>775.8802050736419</v>
       </c>
       <c r="L23" t="n">
-        <v>1417.400205073642</v>
+        <v>993.8163275862049</v>
       </c>
       <c r="M23" t="n">
-        <v>2058.920205073645</v>
+        <v>1635.336327586205</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.549243836214</v>
+        <v>1642.814971748371</v>
       </c>
       <c r="O23" t="n">
-        <v>2393.691050093541</v>
+        <v>1805.956778005698</v>
       </c>
       <c r="P23" t="n">
-        <v>2592</v>
+        <v>2004.265727912157</v>
       </c>
       <c r="Q23" t="n">
         <v>2592</v>
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>492.5458087310154</v>
+        <v>598.9644115421304</v>
       </c>
       <c r="C24" t="n">
-        <v>452.0408466648342</v>
+        <v>558.4594494759493</v>
       </c>
       <c r="D24" t="n">
-        <v>424.8310619196801</v>
+        <v>531.2496647307952</v>
       </c>
       <c r="E24" t="n">
-        <v>402.9400546248188</v>
+        <v>509.3586574359339</v>
       </c>
       <c r="F24" t="n">
-        <v>59.87314317241791</v>
+        <v>490.5341702259573</v>
       </c>
       <c r="G24" t="n">
-        <v>55.83964972137068</v>
+        <v>486.5006767749101</v>
       </c>
       <c r="H24" t="n">
-        <v>51.84</v>
+        <v>245.20236806254</v>
       </c>
       <c r="I24" t="n">
         <v>51.84</v>
@@ -6083,28 +6083,28 @@
         <v>2174.558747796677</v>
       </c>
       <c r="R24" t="n">
-        <v>1886.389711280662</v>
+        <v>1992.808314091777</v>
       </c>
       <c r="S24" t="n">
-        <v>1429.116612402744</v>
+        <v>1859.777639456283</v>
       </c>
       <c r="T24" t="n">
-        <v>1022.703136959095</v>
+        <v>1777.606588255059</v>
       </c>
       <c r="U24" t="n">
-        <v>942.7422723261641</v>
+        <v>1697.645723622128</v>
       </c>
       <c r="V24" t="n">
-        <v>848.2870529407902</v>
+        <v>1603.190504236754</v>
       </c>
       <c r="W24" t="n">
-        <v>735.7889287894483</v>
+        <v>1166.449955842987</v>
       </c>
       <c r="X24" t="n">
-        <v>635.9275758143093</v>
+        <v>1066.588602867849</v>
       </c>
       <c r="Y24" t="n">
-        <v>556.744350798012</v>
+        <v>663.1629536091269</v>
       </c>
     </row>
     <row r="25">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.4524900262056</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C26" t="n">
-        <v>467.6801887706562</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D26" t="n">
-        <v>377.4386173162624</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E26" t="n">
-        <v>293.2332742790214</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F26" t="n">
-        <v>208.4962755840599</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3120357733081</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H26" t="n">
         <v>51.92</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T26" t="n">
-        <v>2190.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X26" t="n">
-        <v>952.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y26" t="n">
-        <v>760.0780586682001</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>274.8019872997061</v>
+        <v>816.8682329734396</v>
       </c>
       <c r="C27" t="n">
-        <v>234.297025233525</v>
+        <v>452.1208466648342</v>
       </c>
       <c r="D27" t="n">
-        <v>207.0872404883708</v>
+        <v>424.91106191968</v>
       </c>
       <c r="E27" t="n">
-        <v>185.1962331935096</v>
+        <v>78.77763038239456</v>
       </c>
       <c r="F27" t="n">
-        <v>166.371745983533</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G27" t="n">
-        <v>162.3382525324857</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6320,28 +6320,28 @@
         <v>2174.638747796677</v>
       </c>
       <c r="R27" t="n">
-        <v>1668.645889849353</v>
+        <v>1992.888314091777</v>
       </c>
       <c r="S27" t="n">
-        <v>1211.372790971434</v>
+        <v>1753.439036645168</v>
       </c>
       <c r="T27" t="n">
-        <v>1129.20173977021</v>
+        <v>1347.025561201519</v>
       </c>
       <c r="U27" t="n">
-        <v>724.9984508948548</v>
+        <v>1267.064696568588</v>
       </c>
       <c r="V27" t="n">
-        <v>630.543231509481</v>
+        <v>1172.609477183214</v>
       </c>
       <c r="W27" t="n">
-        <v>518.045107358139</v>
+        <v>1060.111353031872</v>
       </c>
       <c r="X27" t="n">
-        <v>418.1837543830001</v>
+        <v>960.2500000567335</v>
       </c>
       <c r="Y27" t="n">
-        <v>339.0005293667027</v>
+        <v>881.0667750404361</v>
       </c>
     </row>
     <row r="28">
@@ -6399,19 +6399,19 @@
         <v>463.9758216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.69634147829413</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
       </c>
       <c r="T28" t="n">
-        <v>159.3041526995475</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U28" t="n">
-        <v>327.6791351738997</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V28" t="n">
-        <v>448.2905280598457</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W28" t="n">
         <v>541.9714463195231</v>
@@ -6454,25 +6454,25 @@
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>560.4418942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K29" t="n">
-        <v>1202.951894293937</v>
+        <v>310.1117798977626</v>
       </c>
       <c r="L29" t="n">
-        <v>1420.8880168065</v>
+        <v>528.0479024103255</v>
       </c>
       <c r="M29" t="n">
-        <v>1420.8880168065</v>
+        <v>1170.557902410326</v>
       </c>
       <c r="N29" t="n">
-        <v>1755.181050093541</v>
+        <v>1813.067902410326</v>
       </c>
       <c r="O29" t="n">
-        <v>2397.691050093541</v>
+        <v>1976.209708667652</v>
       </c>
       <c r="P29" t="n">
-        <v>2596</v>
+        <v>2174.518658574112</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6509,25 +6509,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1001.877593356413</v>
+        <v>1141.110657215864</v>
       </c>
       <c r="C30" t="n">
-        <v>637.1302070478077</v>
+        <v>776.3632709072585</v>
       </c>
       <c r="D30" t="n">
-        <v>609.9204223026536</v>
+        <v>424.91106191968</v>
       </c>
       <c r="E30" t="n">
-        <v>588.0294150077924</v>
+        <v>78.77763038239453</v>
       </c>
       <c r="F30" t="n">
-        <v>569.2049277978158</v>
+        <v>59.95314317241791</v>
       </c>
       <c r="G30" t="n">
-        <v>240.9290101043443</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H30" t="n">
-        <v>236.9293603829736</v>
+        <v>51.92</v>
       </c>
       <c r="I30" t="n">
         <v>51.92</v>
@@ -6557,28 +6557,28 @@
         <v>2253.229505368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1747.236647421212</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S30" t="n">
-        <v>1614.205972785717</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T30" t="n">
-        <v>1532.034921584493</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U30" t="n">
-        <v>1452.074056951562</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V30" t="n">
-        <v>1357.618837566188</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W30" t="n">
-        <v>1245.120713414846</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X30" t="n">
-        <v>1145.259360439707</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y30" t="n">
-        <v>1066.07613542341</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="31">
@@ -6588,19 +6588,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.6672726401017</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C31" t="n">
-        <v>734.4592784585375</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D31" t="n">
-        <v>769.5684225835375</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E31" t="n">
-        <v>809.1873267949505</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F31" t="n">
-        <v>855.338299386886</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G31" t="n">
         <v>926.0259486505795</v>
@@ -6645,19 +6645,19 @@
         <v>164.4325496506081</v>
       </c>
       <c r="U31" t="n">
-        <v>332.8075321249603</v>
+        <v>327.6791351738997</v>
       </c>
       <c r="V31" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2905280598457</v>
       </c>
       <c r="W31" t="n">
-        <v>547.0998432705837</v>
+        <v>541.9714463195231</v>
       </c>
       <c r="X31" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7922373437167</v>
       </c>
       <c r="Y31" t="n">
-        <v>653.1199349738096</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="32">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.4524900262331</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C32" t="n">
-        <v>467.6801887706837</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D32" t="n">
-        <v>377.4386173162899</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E32" t="n">
-        <v>293.2332742790489</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F32" t="n">
-        <v>208.4962755840874</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G32" t="n">
-        <v>126.3120357733355</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6691,52 +6691,52 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>560.4418942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>1202.951894293937</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L32" t="n">
-        <v>1845.461894293937</v>
+        <v>994.8863275862049</v>
       </c>
       <c r="M32" t="n">
-        <v>2234.549243836214</v>
+        <v>1637.396327586206</v>
       </c>
       <c r="N32" t="n">
-        <v>2234.549243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O32" t="n">
-        <v>2397.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2596.000000000027</v>
+        <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.504870856013</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T32" t="n">
-        <v>2190.313881748941</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.8899438109</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.91921232926</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.339943661636</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X32" t="n">
-        <v>952.3178896609613</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y32" t="n">
-        <v>760.0780586682276</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1001.877593356413</v>
+        <v>353.3927448715644</v>
       </c>
       <c r="C33" t="n">
-        <v>961.372631290232</v>
+        <v>127.87842242241</v>
       </c>
       <c r="D33" t="n">
-        <v>934.1628465450779</v>
+        <v>100.6686376772558</v>
       </c>
       <c r="E33" t="n">
-        <v>912.2718392502167</v>
+        <v>78.77763038239456</v>
       </c>
       <c r="F33" t="n">
-        <v>893.44735204024</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G33" t="n">
-        <v>573.5244420263349</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H33" t="n">
-        <v>245.2823680625399</v>
+        <v>51.92</v>
       </c>
       <c r="I33" t="n">
         <v>51.92</v>
@@ -6797,25 +6797,25 @@
         <v>2071.479071663636</v>
       </c>
       <c r="S33" t="n">
-        <v>1614.205972785717</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T33" t="n">
-        <v>1532.034921584493</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U33" t="n">
-        <v>1452.074056951562</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V33" t="n">
-        <v>1357.618837566188</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W33" t="n">
         <v>1245.120713414846</v>
       </c>
       <c r="X33" t="n">
-        <v>1145.259360439707</v>
+        <v>821.0169361972826</v>
       </c>
       <c r="Y33" t="n">
-        <v>1066.07613542341</v>
+        <v>417.591286938561</v>
       </c>
     </row>
     <row r="34">
@@ -6879,19 +6879,19 @@
         <v>51.92</v>
       </c>
       <c r="T34" t="n">
-        <v>159.3041526995475</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U34" t="n">
-        <v>327.6791351738997</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V34" t="n">
-        <v>448.2905280598457</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W34" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X34" t="n">
-        <v>614.7922373437167</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y34" t="n">
         <v>647.991538022749</v>
@@ -6904,13 +6904,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>444.0238605876112</v>
+        <v>444.0238605876114</v>
       </c>
       <c r="C35" t="n">
-        <v>338.4939835744861</v>
+        <v>338.4939835744862</v>
       </c>
       <c r="D35" t="n">
-        <v>272.4948363625166</v>
+        <v>272.4948363625167</v>
       </c>
       <c r="E35" t="n">
         <v>212.5319175676998</v>
@@ -6919,7 +6919,7 @@
         <v>152.0373431151626</v>
       </c>
       <c r="G35" t="n">
-        <v>94.09552754683496</v>
+        <v>94.09552754683497</v>
       </c>
       <c r="H35" t="n">
         <v>44.88</v>
@@ -6931,16 +6931,16 @@
         <v>127.400205073642</v>
       </c>
       <c r="K35" t="n">
-        <v>303.0717798977627</v>
+        <v>553.8331213236512</v>
       </c>
       <c r="L35" t="n">
-        <v>521.0079024103255</v>
+        <v>771.7692438362141</v>
       </c>
       <c r="M35" t="n">
-        <v>1076.397902410326</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N35" t="n">
-        <v>1490.301050093541</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O35" t="n">
         <v>2045.691050093541</v>
@@ -6955,25 +6955,25 @@
         <v>2244</v>
       </c>
       <c r="S35" t="n">
-        <v>2129.379271720422</v>
+        <v>2124.74729509841</v>
       </c>
       <c r="T35" t="n">
-        <v>1891.430706855774</v>
+        <v>1886.798730233762</v>
       </c>
       <c r="U35" t="n">
-        <v>1584.249193160157</v>
+        <v>1579.617216538145</v>
       </c>
       <c r="V35" t="n">
-        <v>1296.520885920941</v>
+        <v>1291.888909298929</v>
       </c>
       <c r="W35" t="n">
-        <v>1000.184041495741</v>
+        <v>995.5520648737293</v>
       </c>
       <c r="X35" t="n">
-        <v>750.404411737491</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y35" t="n">
-        <v>582.4070049871815</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>720.6278899837531</v>
+        <v>411.0270273857892</v>
       </c>
       <c r="C36" t="n">
-        <v>704.3653521599963</v>
+        <v>394.7644895620323</v>
       </c>
       <c r="D36" t="n">
-        <v>701.3979916572664</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="E36" t="n">
-        <v>701.3979916572664</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="F36" t="n">
-        <v>701.3979916572664</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="G36" t="n">
-        <v>373.1220739637949</v>
+        <v>391.7971290593023</v>
       </c>
       <c r="H36" t="n">
-        <v>44.88</v>
+        <v>63.55505509550738</v>
       </c>
       <c r="I36" t="n">
         <v>44.88</v>
@@ -7013,46 +7013,46 @@
         <v>547.1588055149654</v>
       </c>
       <c r="L36" t="n">
-        <v>976.7579942888656</v>
+        <v>976.7579942888729</v>
       </c>
       <c r="M36" t="n">
-        <v>1250.062386031725</v>
+        <v>1250.062386031732</v>
       </c>
       <c r="N36" t="n">
-        <v>1575.52177884684</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O36" t="n">
-        <v>1990.370569304144</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P36" t="n">
-        <v>2244.000000000066</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q36" t="n">
-        <v>2244.000000000066</v>
+        <v>2165.409242428215</v>
       </c>
       <c r="R36" t="n">
-        <v>2086.49199053759</v>
+        <v>2007.901232965739</v>
       </c>
       <c r="S36" t="n">
-        <v>1977.70374014452</v>
+        <v>1899.112982572669</v>
       </c>
       <c r="T36" t="n">
-        <v>1802.300369726985</v>
+        <v>1492.699507129021</v>
       </c>
       <c r="U36" t="n">
-        <v>1398.097080851629</v>
+        <v>1088.496218253665</v>
       </c>
       <c r="V36" t="n">
-        <v>1327.884285708679</v>
+        <v>1018.283423110715</v>
       </c>
       <c r="W36" t="n">
-        <v>891.1437373149132</v>
+        <v>930.0277232017978</v>
       </c>
       <c r="X36" t="n">
-        <v>815.5248085821985</v>
+        <v>854.4087944690831</v>
       </c>
       <c r="Y36" t="n">
-        <v>760.5840078083254</v>
+        <v>450.9831452103615</v>
       </c>
     </row>
     <row r="37">
@@ -7110,7 +7110,7 @@
         <v>408.4509731532439</v>
       </c>
       <c r="R37" t="n">
-        <v>51.41391723586989</v>
+        <v>51.41391723586987</v>
       </c>
       <c r="S37" t="n">
         <v>44.88</v>
@@ -7122,13 +7122,13 @@
         <v>373.2875321249604</v>
       </c>
       <c r="V37" t="n">
-        <v>517.6589250109064</v>
+        <v>397.7131653190144</v>
       </c>
       <c r="W37" t="n">
-        <v>517.6589250109064</v>
+        <v>397.7131653190144</v>
       </c>
       <c r="X37" t="n">
-        <v>517.6589250109064</v>
+        <v>494.2939563432079</v>
       </c>
       <c r="Y37" t="n">
         <v>551.2532570222402</v>
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>439.3918839655994</v>
+        <v>444.0238605876114</v>
       </c>
       <c r="C38" t="n">
-        <v>333.8620069524742</v>
+        <v>338.4939835744862</v>
       </c>
       <c r="D38" t="n">
-        <v>267.8628597405047</v>
+        <v>272.4948363625167</v>
       </c>
       <c r="E38" t="n">
-        <v>207.8999409456879</v>
+        <v>212.5319175676998</v>
       </c>
       <c r="F38" t="n">
-        <v>147.4053664931506</v>
+        <v>152.0373431151626</v>
       </c>
       <c r="G38" t="n">
         <v>94.09552754683497</v>
@@ -7165,16 +7165,16 @@
         <v>44.88</v>
       </c>
       <c r="J38" t="n">
-        <v>127.400205073642</v>
+        <v>553.4018942939372</v>
       </c>
       <c r="K38" t="n">
-        <v>303.0717798977627</v>
+        <v>1108.791894293937</v>
       </c>
       <c r="L38" t="n">
-        <v>521.0079024103255</v>
+        <v>1326.7280168065</v>
       </c>
       <c r="M38" t="n">
-        <v>1076.397902410326</v>
+        <v>1327.159243836214</v>
       </c>
       <c r="N38" t="n">
         <v>1327.159243836214</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>928.7812518052225</v>
+        <v>1101.795089801022</v>
       </c>
       <c r="C39" t="n">
-        <v>912.5187139814657</v>
+        <v>1085.532551977265</v>
       </c>
       <c r="D39" t="n">
-        <v>909.5513534787358</v>
+        <v>734.0803429896864</v>
       </c>
       <c r="E39" t="n">
-        <v>909.5513534787358</v>
+        <v>387.9469114524009</v>
       </c>
       <c r="F39" t="n">
-        <v>566.4844420263349</v>
+        <v>44.88</v>
       </c>
       <c r="G39" t="n">
-        <v>566.4844420263349</v>
+        <v>44.88</v>
       </c>
       <c r="H39" t="n">
-        <v>238.24236806254</v>
+        <v>44.88</v>
       </c>
       <c r="I39" t="n">
         <v>44.88</v>
@@ -7250,46 +7250,46 @@
         <v>547.1588055149654</v>
       </c>
       <c r="L39" t="n">
-        <v>976.7579942887996</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M39" t="n">
-        <v>1250.062386031659</v>
+        <v>1252.251891400195</v>
       </c>
       <c r="N39" t="n">
-        <v>1575.521778846774</v>
+        <v>1575.521778846848</v>
       </c>
       <c r="O39" t="n">
-        <v>1990.370569304078</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P39" t="n">
-        <v>2244</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q39" t="n">
-        <v>2165.409242428142</v>
+        <v>2165.409242428215</v>
       </c>
       <c r="R39" t="n">
-        <v>1828.685760415475</v>
+        <v>2007.901232965739</v>
       </c>
       <c r="S39" t="n">
-        <v>1719.897510022405</v>
+        <v>1892.911348018205</v>
       </c>
       <c r="T39" t="n">
-        <v>1313.484034578757</v>
+        <v>1834.982721059405</v>
       </c>
       <c r="U39" t="n">
-        <v>1257.76559418825</v>
+        <v>1779.264280668898</v>
       </c>
       <c r="V39" t="n">
-        <v>1187.5527990453</v>
+        <v>1709.051485525948</v>
       </c>
       <c r="W39" t="n">
-        <v>1099.297099136382</v>
+        <v>1620.79578561703</v>
       </c>
       <c r="X39" t="n">
-        <v>1023.678170403668</v>
+        <v>1545.176856884316</v>
       </c>
       <c r="Y39" t="n">
-        <v>968.7373696297948</v>
+        <v>1490.236056110443</v>
       </c>
     </row>
     <row r="40">
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>381.3863753602982</v>
+        <v>387.5849231266184</v>
       </c>
       <c r="C40" t="n">
-        <v>381.3863753602982</v>
+        <v>459.1369289450541</v>
       </c>
       <c r="D40" t="n">
-        <v>397.4317446319681</v>
+        <v>518.0060730700542</v>
       </c>
       <c r="E40" t="n">
-        <v>460.8106488433811</v>
+        <v>581.3849772814672</v>
       </c>
       <c r="F40" t="n">
-        <v>530.7216214353166</v>
+        <v>651.2959498734027</v>
       </c>
       <c r="G40" t="n">
-        <v>630.2976676500707</v>
+        <v>750.8719960881568</v>
       </c>
       <c r="H40" t="n">
         <v>750.8719960881568</v>
@@ -7356,19 +7356,19 @@
         <v>44.88</v>
       </c>
       <c r="U40" t="n">
-        <v>237.0149824743522</v>
+        <v>44.88</v>
       </c>
       <c r="V40" t="n">
-        <v>381.3863753602982</v>
+        <v>189.251392885946</v>
       </c>
       <c r="W40" t="n">
-        <v>381.3863753602982</v>
+        <v>306.6923111456234</v>
       </c>
       <c r="X40" t="n">
-        <v>381.3863753602982</v>
+        <v>306.6923111456234</v>
       </c>
       <c r="Y40" t="n">
-        <v>381.3863753602982</v>
+        <v>330.2775854603262</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.0238605876114</v>
+        <v>439.3918839655994</v>
       </c>
       <c r="C41" t="n">
-        <v>338.4939835744862</v>
+        <v>333.8620069524742</v>
       </c>
       <c r="D41" t="n">
-        <v>272.4948363625167</v>
+        <v>267.8628597405047</v>
       </c>
       <c r="E41" t="n">
-        <v>212.5319175676998</v>
+        <v>207.8999409456879</v>
       </c>
       <c r="F41" t="n">
-        <v>152.0373431151626</v>
+        <v>147.4053664931506</v>
       </c>
       <c r="G41" t="n">
         <v>94.09552754683497</v>
@@ -7408,19 +7408,19 @@
         <v>682.790205073642</v>
       </c>
       <c r="L41" t="n">
-        <v>900.7263275862049</v>
+        <v>1238.180205073642</v>
       </c>
       <c r="M41" t="n">
-        <v>1327.159243836214</v>
+        <v>1793.570205073642</v>
       </c>
       <c r="N41" t="n">
-        <v>1327.159243836214</v>
+        <v>1882.549243836214</v>
       </c>
       <c r="O41" t="n">
-        <v>1490.301050093541</v>
+        <v>2045.691050093541</v>
       </c>
       <c r="P41" t="n">
-        <v>1688.61</v>
+        <v>2244</v>
       </c>
       <c r="Q41" t="n">
         <v>2244</v>
@@ -7444,10 +7444,10 @@
         <v>995.5520648737293</v>
       </c>
       <c r="X41" t="n">
-        <v>750.404411737491</v>
+        <v>745.7724351154791</v>
       </c>
       <c r="Y41" t="n">
-        <v>582.4070049871816</v>
+        <v>577.7750283651696</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>141.1329364727258</v>
+        <v>64.1098983264868</v>
       </c>
       <c r="C42" t="n">
-        <v>124.8703986489689</v>
+        <v>47.84736050272993</v>
       </c>
       <c r="D42" t="n">
-        <v>121.903038146239</v>
+        <v>44.88</v>
       </c>
       <c r="E42" t="n">
-        <v>121.903038146239</v>
+        <v>44.88</v>
       </c>
       <c r="F42" t="n">
-        <v>121.903038146239</v>
+        <v>44.88</v>
       </c>
       <c r="G42" t="n">
-        <v>121.903038146239</v>
+        <v>44.88</v>
       </c>
       <c r="H42" t="n">
-        <v>121.903038146239</v>
+        <v>44.88</v>
       </c>
       <c r="I42" t="n">
         <v>44.88</v>
@@ -7487,46 +7487,46 @@
         <v>547.1588055149654</v>
       </c>
       <c r="L42" t="n">
-        <v>976.7579942888583</v>
+        <v>978.9474996573354</v>
       </c>
       <c r="M42" t="n">
-        <v>1250.062386031718</v>
+        <v>1250.06238603171</v>
       </c>
       <c r="N42" t="n">
-        <v>1575.521778846833</v>
+        <v>1575.521778846826</v>
       </c>
       <c r="O42" t="n">
-        <v>1990.370569304137</v>
+        <v>1990.37056930413</v>
       </c>
       <c r="P42" t="n">
-        <v>2244.000000000059</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="R42" t="n">
-        <v>1738.007142052676</v>
+        <v>2086.491990537575</v>
       </c>
       <c r="S42" t="n">
-        <v>1629.218891659606</v>
+        <v>1629.218891659657</v>
       </c>
       <c r="T42" t="n">
-        <v>1222.805416215957</v>
+        <v>1494.267226554567</v>
       </c>
       <c r="U42" t="n">
-        <v>818.6021273406018</v>
+        <v>1090.063937679211</v>
       </c>
       <c r="V42" t="n">
-        <v>748.3893321976522</v>
+        <v>671.3662940514131</v>
       </c>
       <c r="W42" t="n">
-        <v>311.6487838038859</v>
+        <v>583.1105941424954</v>
       </c>
       <c r="X42" t="n">
-        <v>236.0298550711712</v>
+        <v>159.0068169249322</v>
       </c>
       <c r="Y42" t="n">
-        <v>181.0890542972982</v>
+        <v>104.0660161510591</v>
       </c>
     </row>
     <row r="43">
@@ -7536,31 +7536,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>843.0486473012365</v>
+        <v>788.9879719610695</v>
       </c>
       <c r="C43" t="n">
-        <v>914.6006531196723</v>
+        <v>860.5399777795053</v>
       </c>
       <c r="D43" t="n">
-        <v>973.4697972446723</v>
+        <v>881.2062073483729</v>
       </c>
       <c r="E43" t="n">
-        <v>1036.848701456085</v>
+        <v>944.5851115597859</v>
       </c>
       <c r="F43" t="n">
-        <v>1106.759674048021</v>
+        <v>1014.496084151721</v>
       </c>
       <c r="G43" t="n">
-        <v>1106.759674048021</v>
+        <v>1114.072130366475</v>
       </c>
       <c r="H43" t="n">
-        <v>1106.759674048021</v>
+        <v>1234.646458804561</v>
       </c>
       <c r="I43" t="n">
-        <v>1292.072015934923</v>
+        <v>1419.958800691464</v>
       </c>
       <c r="J43" t="n">
-        <v>1300.953015767703</v>
+        <v>1428.839800524243</v>
       </c>
       <c r="K43" t="n">
         <v>1428.839800524243</v>
@@ -7605,7 +7605,7 @@
         <v>731.6806342947774</v>
       </c>
       <c r="Y43" t="n">
-        <v>788.6399349738097</v>
+        <v>731.6806342947774</v>
       </c>
     </row>
     <row r="44">
@@ -7639,22 +7639,22 @@
         <v>44.88</v>
       </c>
       <c r="J44" t="n">
-        <v>127.400205073642</v>
+        <v>553.4018942939372</v>
       </c>
       <c r="K44" t="n">
-        <v>303.0717798977627</v>
+        <v>729.0734691180577</v>
       </c>
       <c r="L44" t="n">
-        <v>521.0079024103255</v>
+        <v>970.0781937426734</v>
       </c>
       <c r="M44" t="n">
-        <v>1076.397902410326</v>
+        <v>970.0781937426734</v>
       </c>
       <c r="N44" t="n">
-        <v>1327.159243836214</v>
+        <v>970.0781937426734</v>
       </c>
       <c r="O44" t="n">
-        <v>1490.301050093541</v>
+        <v>1133.22</v>
       </c>
       <c r="P44" t="n">
         <v>1688.61</v>
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>761.0795952961838</v>
+        <v>1186.58748192733</v>
       </c>
       <c r="C45" t="n">
-        <v>396.3322089875784</v>
+        <v>821.8400956187243</v>
       </c>
       <c r="D45" t="n">
-        <v>44.88</v>
+        <v>470.3878866311458</v>
       </c>
       <c r="E45" t="n">
-        <v>44.88</v>
+        <v>124.2544550938603</v>
       </c>
       <c r="F45" t="n">
-        <v>44.88</v>
+        <v>124.2544550938603</v>
       </c>
       <c r="G45" t="n">
-        <v>44.88</v>
+        <v>124.2544550938603</v>
       </c>
       <c r="H45" t="n">
-        <v>44.88</v>
+        <v>124.2544550938603</v>
       </c>
       <c r="I45" t="n">
         <v>44.88</v>
@@ -7724,46 +7724,46 @@
         <v>547.1588055149654</v>
       </c>
       <c r="L45" t="n">
-        <v>978.9474996573354</v>
+        <v>976.7579942888583</v>
       </c>
       <c r="M45" t="n">
-        <v>1250.062386031659</v>
+        <v>1250.062386031718</v>
       </c>
       <c r="N45" t="n">
-        <v>1575.521778846774</v>
+        <v>1575.521778846833</v>
       </c>
       <c r="O45" t="n">
-        <v>1990.370569304078</v>
+        <v>1990.370569304137</v>
       </c>
       <c r="P45" t="n">
-        <v>2244</v>
+        <v>2244.000000000059</v>
       </c>
       <c r="Q45" t="n">
-        <v>2166.976961853761</v>
+        <v>2244.000000000059</v>
       </c>
       <c r="R45" t="n">
-        <v>2009.468952391285</v>
+        <v>2086.491990537583</v>
       </c>
       <c r="S45" t="n">
-        <v>1552.195853513367</v>
+        <v>1977.703740144512</v>
       </c>
       <c r="T45" t="n">
-        <v>1494.267226554567</v>
+        <v>1919.775113185713</v>
       </c>
       <c r="U45" t="n">
-        <v>1438.54878616406</v>
+        <v>1864.056672795206</v>
       </c>
       <c r="V45" t="n">
-        <v>1368.33599102111</v>
+        <v>1793.843877652256</v>
       </c>
       <c r="W45" t="n">
-        <v>1280.080291112192</v>
+        <v>1705.588177743338</v>
       </c>
       <c r="X45" t="n">
-        <v>1204.461362379478</v>
+        <v>1629.969249010624</v>
       </c>
       <c r="Y45" t="n">
-        <v>1149.520561605605</v>
+        <v>1226.543599751902</v>
       </c>
     </row>
     <row r="46">
@@ -7773,31 +7773,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>845.9472726401018</v>
+        <v>500.2721984625236</v>
       </c>
       <c r="C46" t="n">
-        <v>917.4992784585376</v>
+        <v>571.8242042809594</v>
       </c>
       <c r="D46" t="n">
-        <v>976.3684225835376</v>
+        <v>571.8242042809594</v>
       </c>
       <c r="E46" t="n">
-        <v>1039.747326794951</v>
+        <v>635.2031084923724</v>
       </c>
       <c r="F46" t="n">
-        <v>1109.658299386886</v>
+        <v>705.1140810843078</v>
       </c>
       <c r="G46" t="n">
-        <v>1209.23434560164</v>
+        <v>765.2096740480209</v>
       </c>
       <c r="H46" t="n">
-        <v>1329.808674039726</v>
+        <v>765.2096740480209</v>
       </c>
       <c r="I46" t="n">
-        <v>1419.958800691464</v>
+        <v>950.5220159349235</v>
       </c>
       <c r="J46" t="n">
-        <v>1428.839800524243</v>
+        <v>1300.953015767703</v>
       </c>
       <c r="K46" t="n">
         <v>1428.839800524243</v>
@@ -7830,19 +7830,19 @@
         <v>181.1525496506081</v>
       </c>
       <c r="U46" t="n">
-        <v>373.2875321249604</v>
+        <v>181.1525496506081</v>
       </c>
       <c r="V46" t="n">
-        <v>517.6589250109064</v>
+        <v>325.5239425365541</v>
       </c>
       <c r="W46" t="n">
-        <v>635.0998432705838</v>
+        <v>442.9648607962315</v>
       </c>
       <c r="X46" t="n">
-        <v>731.6806342947774</v>
+        <v>442.9648607962315</v>
       </c>
       <c r="Y46" t="n">
-        <v>788.6399349738097</v>
+        <v>442.9648607962315</v>
       </c>
     </row>
   </sheetData>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>653.1724032050533</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>777.3653500296342</v>
+        <v>584.9827562456367</v>
       </c>
       <c r="O2" t="n">
         <v>0.4816735941929551</v>
@@ -8204,13 +8204,13 @@
         <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>181.6174062160024</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>845.554996989051</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N5" t="n">
         <v>777.3653500296342</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>309.7251508449954</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,13 +8444,13 @@
         <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>845.554996989051</v>
+        <v>771.1871117477669</v>
       </c>
       <c r="N8" t="n">
-        <v>637.6540577531742</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
         <v>0.4816735941929551</v>
@@ -8678,13 +8678,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>947.3167457327718</v>
+        <v>524.5661951690028</v>
       </c>
       <c r="N11" t="n">
         <v>228.3401037984784</v>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>47.80341426035164</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>423.7791327534228</v>
       </c>
       <c r="M14" t="n">
-        <v>299.3167457327696</v>
+        <v>947.3167457327697</v>
       </c>
       <c r="N14" t="n">
-        <v>228.3401037984784</v>
+        <v>876.3401037984784</v>
       </c>
       <c r="O14" t="n">
-        <v>248.1154848729362</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>447.6879293874176</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,13 +9152,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>427.8625025125627</v>
       </c>
       <c r="M17" t="n">
-        <v>690.3746745633521</v>
+        <v>567.2576574805605</v>
       </c>
       <c r="N17" t="n">
         <v>228.3401037984784</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>299.3167457327696</v>
+        <v>947.3167457327697</v>
       </c>
       <c r="N20" t="n">
-        <v>228.3401037984784</v>
+        <v>706.4482546449888</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>225.2494494362331</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9629,13 +9629,13 @@
         <v>470.5539648241206</v>
       </c>
       <c r="L23" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>947.3167457327725</v>
+        <v>947.3167457327697</v>
       </c>
       <c r="N23" t="n">
-        <v>401.7027692152149</v>
+        <v>235.8942898208684</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>471.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N29" t="n">
-        <v>566.0098343914492</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O29" t="n">
-        <v>484.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.18109136266131</v>
+        <v>447.9198200756798</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>471.5539648241206</v>
       </c>
       <c r="L32" t="n">
-        <v>428.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>692.3342705229481</v>
+        <v>948.3167457327706</v>
       </c>
       <c r="N32" t="n">
-        <v>228.3401037984784</v>
+        <v>237.8538857804631</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>253.2942842685744</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,10 +10583,10 @@
         <v>860.3167457327697</v>
       </c>
       <c r="N35" t="n">
-        <v>646.4240913572821</v>
+        <v>789.3401037984784</v>
       </c>
       <c r="O35" t="n">
-        <v>396.2102967097708</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -10656,7 +10656,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>385.8777148754853</v>
+        <v>385.8777148754926</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>383.5539648241206</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>860.3167457327697</v>
+        <v>299.7523285910667</v>
       </c>
       <c r="N38" t="n">
-        <v>481.634388067053</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10893,13 +10893,13 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>385.8777148754186</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870447</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11051,13 +11051,13 @@
         <v>383.5539648241206</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>340.8625025125627</v>
       </c>
       <c r="M41" t="n">
-        <v>730.0570651772234</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N41" t="n">
-        <v>228.3401037984784</v>
+        <v>318.2179207303693</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>583.1810913626613</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,10 +11130,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>385.8777148754779</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>469.4831988457798</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>23.30161829500298</v>
       </c>
       <c r="M44" t="n">
-        <v>860.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N44" t="n">
-        <v>481.634388067053</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>360.6879293874151</v>
       </c>
       <c r="Q44" t="n">
         <v>583.1810913626613</v>
@@ -11367,10 +11367,10 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754779</v>
       </c>
       <c r="M45" t="n">
-        <v>469.483198845728</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
         <v>485.4085271713503</v>
@@ -22581,7 +22581,7 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.051603248924948e-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -23238,10 +23238,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.95605685579163</v>
       </c>
       <c r="H11" t="n">
-        <v>2.95605685579163</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23469,7 +23469,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2.956056855791644</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.956056855791758</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23712,10 +23712,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.95605685579163</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.956056855791445</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -24174,7 +24174,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2.956056855791601</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.95605685579163</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>4.585656855791797</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4.585656855791854</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>4.585656855791797</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.585656855791843</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25608,7 +25608,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4.585656855791843</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4.585656855791882</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -26293,16 +26293,16 @@
         <v>1416534.455482733</v>
       </c>
       <c r="J2" t="n">
-        <v>1416799.17037417</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="K2" t="n">
         <v>1416799.170374169</v>
       </c>
       <c r="L2" t="n">
-        <v>1416799.170374169</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="M2" t="n">
-        <v>1416388.524802734</v>
+        <v>1416388.524802733</v>
       </c>
       <c r="N2" t="n">
         <v>1416388.524802733</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044577</v>
+        <v>599959.4017938485</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.404775654</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>513949.0290844531</v>
+        <v>513751.7523916513</v>
       </c>
       <c r="F4" t="n">
-        <v>512264.4313324891</v>
+        <v>512067.1546396872</v>
       </c>
       <c r="G4" t="n">
-        <v>510577.5088988312</v>
+        <v>510380.2322060294</v>
       </c>
       <c r="H4" t="n">
-        <v>508888.2451130981</v>
+        <v>508690.9684202962</v>
       </c>
       <c r="I4" t="n">
-        <v>507196.6230877017</v>
+        <v>506999.3463949</v>
       </c>
       <c r="J4" t="n">
-        <v>505559.8209559914</v>
+        <v>505362.3521738978</v>
       </c>
       <c r="K4" t="n">
-        <v>503863.6019243026</v>
+        <v>503666.133142209</v>
       </c>
       <c r="L4" t="n">
-        <v>502164.9728882493</v>
+        <v>501967.5041061556</v>
       </c>
       <c r="M4" t="n">
-        <v>506489.4162279234</v>
+        <v>506308.908453467</v>
       </c>
       <c r="N4" t="n">
-        <v>504723.3213042065</v>
+        <v>504542.8135297495</v>
       </c>
       <c r="O4" t="n">
-        <v>502954.6717247891</v>
+        <v>502774.1639503329</v>
       </c>
       <c r="P4" t="n">
-        <v>501183.4482814748</v>
+        <v>501002.940507018</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>523947.1130121049</v>
+        <v>524146.2045227144</v>
       </c>
       <c r="C6" t="n">
-        <v>758028.4770697113</v>
+        <v>758227.568580321</v>
       </c>
       <c r="D6" t="n">
-        <v>760039.5655985151</v>
+        <v>760238.6571091242</v>
       </c>
       <c r="E6" t="n">
-        <v>237488.2773982798</v>
+        <v>237685.5540910815</v>
       </c>
       <c r="F6" t="n">
-        <v>830320.8751502441</v>
+        <v>830518.1518430461</v>
       </c>
       <c r="G6" t="n">
-        <v>832007.797583902</v>
+        <v>832205.0742767034</v>
       </c>
       <c r="H6" t="n">
-        <v>833697.0613696349</v>
+        <v>833894.3380624373</v>
       </c>
       <c r="I6" t="n">
-        <v>835388.6833950317</v>
+        <v>835585.9600878335</v>
       </c>
       <c r="J6" t="n">
-        <v>448429.4004181783</v>
+        <v>448626.8692002714</v>
       </c>
       <c r="K6" t="n">
-        <v>838925.6194498666</v>
+        <v>839123.0882319604</v>
       </c>
       <c r="L6" t="n">
-        <v>840624.2484859197</v>
+        <v>840821.7172680143</v>
       </c>
       <c r="M6" t="n">
-        <v>754549.9035748107</v>
+        <v>754730.4113492661</v>
       </c>
       <c r="N6" t="n">
-        <v>840987.998498527</v>
+        <v>841168.5062729839</v>
       </c>
       <c r="O6" t="n">
-        <v>585956.6480779442</v>
+        <v>586137.1558524001</v>
       </c>
       <c r="P6" t="n">
-        <v>844527.8715212591</v>
+        <v>844708.3792957157</v>
       </c>
     </row>
   </sheetData>
@@ -26999,7 +26999,7 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>222.9148456338336</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>64.80590797460354</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>292.192542744412</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.19578428848864</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="4">
@@ -27594,10 +27594,10 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>390.0735599589419</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27612,7 +27612,7 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.047816275856</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>396.1372930982029</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>361.996489594709</v>
       </c>
       <c r="U4" t="n">
         <v>150.9482601269169</v>
@@ -27685,13 +27685,13 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>240.8175776622348</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,19 +27806,19 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>96.05199687804776</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,19 +27828,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>281.3788946195025</v>
       </c>
       <c r="G7" t="n">
         <v>244.858135136612</v>
@@ -27849,16 +27849,16 @@
         <v>227.1197490524383</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
         <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27894,10 +27894,10 @@
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>395.4647967619968</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.858135136612</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.047816275856</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>134.019626433806</v>
+        <v>122.6068625706611</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28226,16 +28226,16 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28244,7 +28244,7 @@
         <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28280,7 +28280,7 @@
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>8.269477602770962</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
@@ -28289,10 +28289,10 @@
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>215.645583216996</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28314,7 +28314,7 @@
         <v>321</v>
       </c>
       <c r="F13" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="G13" t="n">
         <v>321</v>
@@ -28326,7 +28326,7 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K13" t="n">
         <v>321</v>
@@ -28505,25 +28505,25 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>215.6455832169961</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>137.8407332208563</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -28539,7 +28539,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="C16" t="n">
         <v>321</v>
@@ -28602,7 +28602,7 @@
         <v>321</v>
       </c>
       <c r="W16" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="X16" t="n">
         <v>321</v>
@@ -28697,13 +28697,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E18" t="n">
         <v>321</v>
@@ -28742,10 +28742,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R18" t="n">
-        <v>215.6455832169961</v>
+        <v>321</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28757,16 +28757,16 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
     </row>
     <row r="19">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>321</v>
@@ -28943,10 +28943,10 @@
         <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -28988,22 +28988,22 @@
         <v>321</v>
       </c>
       <c r="T21" t="n">
-        <v>215.6455832169959</v>
+        <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="W21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29019,7 +29019,7 @@
         <v>321</v>
       </c>
       <c r="D22" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="E22" t="n">
         <v>321</v>
@@ -29082,7 +29082,7 @@
         <v>321</v>
       </c>
       <c r="Y22" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="23">
@@ -29183,16 +29183,16 @@
         <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
       </c>
       <c r="H24" t="n">
-        <v>321</v>
+        <v>86.07432759891057</v>
       </c>
       <c r="I24" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29219,13 +29219,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>215.6455832169961</v>
+        <v>321</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U24" t="n">
         <v>321</v>
@@ -29234,13 +29234,13 @@
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29347,7 +29347,7 @@
         <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320.0752568557916</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>96.3013908384635</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29411,13 +29411,13 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29426,7 +29426,7 @@
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>215.6455832169961</v>
+        <v>321</v>
       </c>
       <c r="I27" t="n">
         <v>191.4287443819146</v>
@@ -29456,16 +29456,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>215.6455832169961</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
@@ -29541,16 +29541,16 @@
         <v>321</v>
       </c>
       <c r="T28" t="n">
+        <v>321</v>
+      </c>
+      <c r="U28" t="n">
+        <v>321</v>
+      </c>
+      <c r="V28" t="n">
+        <v>321</v>
+      </c>
+      <c r="W28" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="U28" t="n">
-        <v>321</v>
-      </c>
-      <c r="V28" t="n">
-        <v>321</v>
-      </c>
-      <c r="W28" t="n">
-        <v>321</v>
       </c>
       <c r="X28" t="n">
         <v>321</v>
@@ -29645,28 +29645,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>321</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H30" t="n">
         <v>321</v>
       </c>
       <c r="I30" t="n">
-        <v>8.269477602770678</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29693,7 +29693,7 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
         <v>321</v>
@@ -29739,49 +29739,49 @@
         <v>321</v>
       </c>
       <c r="G31" t="n">
+        <v>321</v>
+      </c>
+      <c r="H31" t="n">
+        <v>321</v>
+      </c>
+      <c r="I31" t="n">
+        <v>321</v>
+      </c>
+      <c r="J31" t="n">
+        <v>321</v>
+      </c>
+      <c r="K31" t="n">
+        <v>321</v>
+      </c>
+      <c r="L31" t="n">
+        <v>321</v>
+      </c>
+      <c r="M31" t="n">
+        <v>321</v>
+      </c>
+      <c r="N31" t="n">
+        <v>321</v>
+      </c>
+      <c r="O31" t="n">
+        <v>321</v>
+      </c>
+      <c r="P31" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>321</v>
+      </c>
+      <c r="R31" t="n">
+        <v>321</v>
+      </c>
+      <c r="S31" t="n">
+        <v>321</v>
+      </c>
+      <c r="T31" t="n">
+        <v>321</v>
+      </c>
+      <c r="U31" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="H31" t="n">
-        <v>321</v>
-      </c>
-      <c r="I31" t="n">
-        <v>321</v>
-      </c>
-      <c r="J31" t="n">
-        <v>321</v>
-      </c>
-      <c r="K31" t="n">
-        <v>321</v>
-      </c>
-      <c r="L31" t="n">
-        <v>321</v>
-      </c>
-      <c r="M31" t="n">
-        <v>321</v>
-      </c>
-      <c r="N31" t="n">
-        <v>321</v>
-      </c>
-      <c r="O31" t="n">
-        <v>321</v>
-      </c>
-      <c r="P31" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>321</v>
-      </c>
-      <c r="R31" t="n">
-        <v>321</v>
-      </c>
-      <c r="S31" t="n">
-        <v>321</v>
-      </c>
-      <c r="T31" t="n">
-        <v>321</v>
-      </c>
-      <c r="U31" t="n">
-        <v>321</v>
       </c>
       <c r="V31" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.0752568557645</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.3013908384635</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.2515083760602</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S32" t="n">
-        <v>321</v>
+        <v>320.0752568557917</v>
       </c>
       <c r="T32" t="n">
         <v>321</v>
@@ -29885,7 +29885,7 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
@@ -29897,13 +29897,13 @@
         <v>321</v>
       </c>
       <c r="G33" t="n">
-        <v>8.269477602770678</v>
+        <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29933,7 +29933,7 @@
         <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T33" t="n">
         <v>321</v>
@@ -29945,13 +29945,13 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -30015,7 +30015,7 @@
         <v>321</v>
       </c>
       <c r="T34" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="U34" t="n">
         <v>321</v>
@@ -30030,7 +30030,7 @@
         <v>321</v>
       </c>
       <c r="Y34" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="35">
@@ -30134,13 +30134,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>191.4287443819146</v>
+        <v>172.9404398373622</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>345</v>
@@ -30173,7 +30173,7 @@
         <v>345</v>
       </c>
       <c r="T36" t="n">
-        <v>228.7000039758522</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -30182,13 +30182,13 @@
         <v>345</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="X36" t="n">
         <v>345</v>
       </c>
       <c r="Y36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30258,16 +30258,16 @@
         <v>345</v>
       </c>
       <c r="V37" t="n">
-        <v>345</v>
+        <v>223.8426669778869</v>
       </c>
       <c r="W37" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>321.3990215477793</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30356,16 +30356,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30374,10 +30374,10 @@
         <v>324.9931585165368</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,13 +30404,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>167.5766821753115</v>
+        <v>345</v>
       </c>
       <c r="S39" t="n">
+        <v>338.8603817910803</v>
+      </c>
+      <c r="T39" t="n">
         <v>345</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>345</v>
@@ -30435,13 +30435,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>287.1138003370787</v>
+        <v>345</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D40" t="n">
-        <v>301.7436617643129</v>
+        <v>345</v>
       </c>
       <c r="E40" t="n">
         <v>345</v>
@@ -30453,7 +30453,7 @@
         <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>345</v>
+        <v>223.2077490524383</v>
       </c>
       <c r="I40" t="n">
         <v>345</v>
@@ -30492,19 +30492,19 @@
         <v>207.3509599488807</v>
       </c>
       <c r="U40" t="n">
-        <v>345</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V40" t="n">
         <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>311.2888622582531</v>
       </c>
     </row>
     <row r="41">
@@ -30614,7 +30614,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I42" t="n">
-        <v>115.1759366171379</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,28 +30638,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77.80484999608188</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>268.7471922351727</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
         <v>345</v>
       </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>345</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
       <c r="X42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>345</v>
@@ -30672,13 +30672,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>342.0720956173078</v>
+        <v>345</v>
       </c>
       <c r="C43" t="n">
         <v>345</v>
       </c>
       <c r="D43" t="n">
-        <v>345</v>
+        <v>306.411197418048</v>
       </c>
       <c r="E43" t="n">
         <v>345</v>
@@ -30687,10 +30687,10 @@
         <v>345</v>
       </c>
       <c r="G43" t="n">
-        <v>244.418135136612</v>
+        <v>345</v>
       </c>
       <c r="H43" t="n">
-        <v>223.2077490524383</v>
+        <v>345</v>
       </c>
       <c r="I43" t="n">
         <v>345</v>
@@ -30699,7 +30699,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>345</v>
+        <v>215.821429538848</v>
       </c>
       <c r="L43" t="n">
         <v>330.5174970102382</v>
@@ -30741,7 +30741,7 @@
         <v>345</v>
       </c>
       <c r="Y43" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -30839,7 +30839,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
@@ -30851,7 +30851,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
-        <v>191.4287443819146</v>
+        <v>112.8480338389928</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,13 +30875,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.552042231363501</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R45" t="n">
         <v>345</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="T45" t="n">
         <v>345</v>
@@ -30899,7 +30899,7 @@
         <v>345</v>
       </c>
       <c r="Y45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -30915,7 +30915,7 @@
         <v>345</v>
       </c>
       <c r="D46" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E46" t="n">
         <v>345</v>
@@ -30924,19 +30924,19 @@
         <v>345</v>
       </c>
       <c r="G46" t="n">
+        <v>305.1207542918777</v>
+      </c>
+      <c r="H46" t="n">
+        <v>223.2077490524383</v>
+      </c>
+      <c r="I46" t="n">
         <v>345</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>345</v>
       </c>
-      <c r="I46" t="n">
-        <v>248.8765502675103</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
       <c r="K46" t="n">
-        <v>215.821429538848</v>
+        <v>345</v>
       </c>
       <c r="L46" t="n">
         <v>330.5174970102382</v>
@@ -30966,7 +30966,7 @@
         <v>345</v>
       </c>
       <c r="U46" t="n">
-        <v>345</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V46" t="n">
         <v>345</v>
@@ -30975,10 +30975,10 @@
         <v>345</v>
       </c>
       <c r="X46" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y46" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
   </sheetData>
@@ -34752,10 +34752,10 @@
         <v>65.34340703517586</v>
       </c>
       <c r="M2" t="n">
+        <v>374</v>
+      </c>
+      <c r="N2" t="n">
         <v>181.6174062160025</v>
-      </c>
-      <c r="N2" t="n">
-        <v>374</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34880,10 +34880,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5373419033864</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34898,7 +34898,7 @@
         <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
         <v>374</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7690400511193</v>
+        <v>152.7655296458283</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34983,13 +34983,13 @@
         <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>52.67130150753769</v>
+        <v>234.2887077235401</v>
       </c>
       <c r="L5" t="n">
-        <v>65.34340703517586</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>374</v>
@@ -35001,7 +35001,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>181.6174062160025</v>
+        <v>374</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,19 +35114,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>6.996038651760555</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -35135,16 +35135,16 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4.06650298976183</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>249.0517398730831</v>
@@ -35180,10 +35180,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>148.0211513318892</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35223,13 +35223,13 @@
         <v>373.9999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517591</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>299.6321147587159</v>
       </c>
       <c r="N8" t="n">
-        <v>234.28870772354</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
-        <v>111.8823333356032</v>
+        <v>100.4695694724582</v>
       </c>
       <c r="K10" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.06650298976183</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,13 +35457,13 @@
         <v>513.658479084785</v>
       </c>
       <c r="K11" t="n">
-        <v>177.4460351758794</v>
+        <v>648</v>
       </c>
       <c r="L11" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M11" t="n">
-        <v>648.0000000000022</v>
+        <v>225.2494494362332</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -35472,7 +35472,7 @@
         <v>164.7897032902292</v>
       </c>
       <c r="P11" t="n">
-        <v>248.1154848729366</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q11" t="n">
         <v>593.6709819069124</v>
@@ -35600,7 +35600,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F13" t="n">
-        <v>46.61714403225807</v>
+        <v>41.43694509179277</v>
       </c>
       <c r="G13" t="n">
         <v>76.58186486338801</v>
@@ -35612,7 +35612,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J13" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K13" t="n">
         <v>105.178570461152</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K14" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L14" t="n">
-        <v>220.1374974874373</v>
+        <v>643.9166302408599</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="O14" t="n">
-        <v>412.9051881631653</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P14" t="n">
-        <v>648.0000000000025</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q14" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35825,7 +35825,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33.88619966292134</v>
+        <v>28.7060007224561</v>
       </c>
       <c r="C16" t="n">
         <v>48.27475335195533</v>
@@ -35888,7 +35888,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W16" t="n">
-        <v>89.44699122082511</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X16" t="n">
         <v>73.55635456989245</v>
@@ -35931,13 +35931,13 @@
         <v>513.658479084785</v>
       </c>
       <c r="K17" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L17" t="n">
         <v>648</v>
       </c>
       <c r="M17" t="n">
-        <v>391.0579288305826</v>
+        <v>267.940911747791</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -35949,7 +35949,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K20" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L20" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>478.1081508465103</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P20" t="n">
-        <v>425.5615200488181</v>
+        <v>200.3120706125849</v>
       </c>
       <c r="Q20" t="n">
         <v>593.6709819069124</v>
@@ -36305,7 +36305,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D22" t="n">
-        <v>30.28358300397924</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E22" t="n">
         <v>40.01909516304346</v>
@@ -36368,7 +36368,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="23">
@@ -36408,13 +36408,13 @@
         <v>648</v>
       </c>
       <c r="L23" t="n">
+        <v>220.1374974874373</v>
+      </c>
+      <c r="M23" t="n">
         <v>648</v>
       </c>
-      <c r="M23" t="n">
-        <v>648.000000000003</v>
-      </c>
       <c r="N23" t="n">
-        <v>173.3626654167364</v>
+        <v>7.55418602239002</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36423,7 +36423,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U28" t="n">
         <v>170.0757398730831</v>
@@ -36836,7 +36836,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W28" t="n">
-        <v>94.62719016129032</v>
+        <v>89.44699122082505</v>
       </c>
       <c r="X28" t="n">
         <v>73.55635456989245</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L29" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>337.6697305929707</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>649</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P29" t="n">
         <v>200.3120706125849</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>425.7387287130185</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37025,7 +37025,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>71.40166592292275</v>
+        <v>76.58186486338801</v>
       </c>
       <c r="H31" t="n">
         <v>97.79225094756171</v>
@@ -37067,7 +37067,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U31" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326178</v>
       </c>
       <c r="V31" t="n">
         <v>121.8296897837838</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
         <v>649</v>
       </c>
       <c r="L32" t="n">
-        <v>649</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M32" t="n">
-        <v>393.0175247901786</v>
+        <v>649.000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>9.513781981984657</v>
       </c>
       <c r="O32" t="n">
         <v>164.7897032902292</v>
@@ -37134,7 +37134,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U34" t="n">
         <v>170.0757398730831</v>
@@ -37316,7 +37316,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="35">
@@ -37353,7 +37353,7 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K35" t="n">
-        <v>177.4460351758794</v>
+        <v>430.7403194444537</v>
       </c>
       <c r="L35" t="n">
         <v>220.1374974874373</v>
@@ -37362,10 +37362,10 @@
         <v>561</v>
       </c>
       <c r="N35" t="n">
-        <v>418.0839875588036</v>
+        <v>561</v>
       </c>
       <c r="O35" t="n">
-        <v>561</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P35" t="n">
         <v>200.3120706125849</v>
@@ -37435,7 +37435,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L36" t="n">
-        <v>433.9385745190911</v>
+        <v>433.9385745190985</v>
       </c>
       <c r="M36" t="n">
         <v>276.0650421645042</v>
@@ -37514,7 +37514,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L37" t="n">
-        <v>14.48250298976183</v>
+        <v>14.48250298976181</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37544,16 +37544,16 @@
         <v>194.0757398730831</v>
       </c>
       <c r="V37" t="n">
-        <v>145.8296897837838</v>
+        <v>24.67235676167077</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>33.93366869831696</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K38" t="n">
-        <v>177.4460351758794</v>
+        <v>561</v>
       </c>
       <c r="L38" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M38" t="n">
-        <v>561</v>
+        <v>0.4355828582971078</v>
       </c>
       <c r="N38" t="n">
-        <v>253.2942842685745</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
@@ -37672,13 +37672,13 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L39" t="n">
-        <v>433.9385745190245</v>
+        <v>436.150196103404</v>
       </c>
       <c r="M39" t="n">
         <v>276.0650421645042</v>
       </c>
       <c r="N39" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398451041</v>
       </c>
       <c r="O39" t="n">
         <v>419.0391822801049</v>
@@ -37721,13 +37721,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>16.20744370875745</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
         <v>64.01909516304346</v>
@@ -37739,7 +37739,7 @@
         <v>100.581864863388</v>
       </c>
       <c r="H40" t="n">
-        <v>121.7922509475617</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>187.184183724144</v>
@@ -37778,19 +37778,19 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>194.0757398730831</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>23.82350940879078</v>
       </c>
     </row>
     <row r="41">
@@ -37830,13 +37830,13 @@
         <v>561</v>
       </c>
       <c r="L41" t="n">
-        <v>220.1374974874373</v>
+        <v>561</v>
       </c>
       <c r="M41" t="n">
-        <v>430.7403194444538</v>
+        <v>561</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>89.87781693189082</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,10 +37909,10 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L42" t="n">
-        <v>433.9385745190838</v>
+        <v>436.150196103404</v>
       </c>
       <c r="M42" t="n">
-        <v>276.0650421645042</v>
+        <v>273.8534205801767</v>
       </c>
       <c r="N42" t="n">
         <v>328.7468614294096</v>
@@ -37958,13 +37958,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>54.95829528022917</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C43" t="n">
         <v>72.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>59.46378194444452</v>
+        <v>20.87497936249253</v>
       </c>
       <c r="E43" t="n">
         <v>64.01909516304346</v>
@@ -37973,10 +37973,10 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>100.581864863388</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>121.7922509475617</v>
       </c>
       <c r="I43" t="n">
         <v>187.184183724144</v>
@@ -37985,7 +37985,7 @@
         <v>8.970706901797143</v>
       </c>
       <c r="K43" t="n">
-        <v>129.178570461152</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38027,7 +38027,7 @@
         <v>97.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K44" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L44" t="n">
-        <v>220.1374974874373</v>
+        <v>243.4391157824401</v>
       </c>
       <c r="M44" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>253.2942842685745</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P44" t="n">
-        <v>200.3120706125849</v>
+        <v>561</v>
       </c>
       <c r="Q44" t="n">
         <v>561</v>
@@ -38146,10 +38146,10 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L45" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190838</v>
       </c>
       <c r="M45" t="n">
-        <v>273.8534205801248</v>
+        <v>276.0650421645042</v>
       </c>
       <c r="N45" t="n">
         <v>328.7468614294096</v>
@@ -38201,7 +38201,7 @@
         <v>72.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>64.01909516304346</v>
@@ -38210,19 +38210,19 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>60.70261915526576</v>
       </c>
       <c r="H46" t="n">
-        <v>121.7922509475617</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>91.0607339916543</v>
+        <v>187.184183724144</v>
       </c>
       <c r="J46" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>129.178570461152</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U46" t="n">
-        <v>194.0757398730831</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>145.8296897837838</v>
@@ -38261,10 +38261,10 @@
         <v>118.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
